--- a/hpi_scraper/ContactLevel/no_seed_contacts/contact_level_api_report.xlsx
+++ b/hpi_scraper/ContactLevel/no_seed_contacts/contact_level_api_report.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>1.046 total seed latency</t>
+          <t>1.440 total seed latency</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
